--- a/preferences.xlsx
+++ b/preferences.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uzk-my.sharepoint.com/personal/linus_palm_uzk_onmicrosoft_com/Documents/Master/MA/master-thesis-nurse-scheduling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="375" documentId="13_ncr:1_{4F88A531-D190-2544-BA98-805689BAB8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E806ED04-EA84-C545-ACA6-E3551429EB1A}"/>
+  <xr:revisionPtr revIDLastSave="540" documentId="13_ncr:1_{4F88A531-D190-2544-BA98-805689BAB8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25C1318B-6A97-4B4B-824C-6A91E9F76EAA}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{FADA9CC9-724D-5940-B3C0-8112EB116048}"/>
+    <workbookView xWindow="7240" yWindow="3480" windowWidth="28800" windowHeight="17500" xr2:uid="{FADA9CC9-724D-5940-B3C0-8112EB116048}"/>
   </bookViews>
   <sheets>
     <sheet name="E" sheetId="1" r:id="rId1"/>
@@ -587,280 +587,554 @@
       <c r="A2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
+      <c r="B2" s="4">
+        <v>3</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4">
+        <v>2</v>
+      </c>
+      <c r="E2" s="4">
+        <v>10</v>
+      </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
+      <c r="H2" s="4">
+        <v>4</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0</v>
+      </c>
       <c r="J2" s="4"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="4"/>
+      <c r="B3" s="3">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="4">
+        <v>10</v>
+      </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="3"/>
+      <c r="H3" s="4">
+        <v>4</v>
+      </c>
+      <c r="I3" s="4">
+        <v>1</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+      <c r="B4" s="3">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4">
+        <v>10</v>
+      </c>
+      <c r="F4" s="4">
+        <v>5</v>
+      </c>
       <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="3"/>
+      <c r="H4" s="4">
+        <v>4</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="4"/>
+      <c r="B5" s="3">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3">
+        <v>3</v>
+      </c>
+      <c r="E5" s="4">
+        <v>10</v>
+      </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="3"/>
+      <c r="H5" s="4">
+        <v>4</v>
+      </c>
+      <c r="I5" s="4">
+        <v>1</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="4"/>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3">
+        <v>2</v>
+      </c>
+      <c r="D6" s="3">
+        <v>3</v>
+      </c>
+      <c r="E6" s="4">
+        <v>10</v>
+      </c>
       <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="3"/>
+      <c r="G6" s="4">
+        <v>5</v>
+      </c>
+      <c r="H6" s="4">
+        <v>4</v>
+      </c>
+      <c r="I6" s="4">
+        <v>1</v>
+      </c>
+      <c r="J6" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="4"/>
+      <c r="B7" s="3">
+        <v>3</v>
+      </c>
+      <c r="C7" s="3">
+        <v>2</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4">
+        <v>10</v>
+      </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="3"/>
+      <c r="H7" s="4">
+        <v>4</v>
+      </c>
+      <c r="I7" s="4">
+        <v>1</v>
+      </c>
+      <c r="J7" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="4"/>
+      <c r="B8" s="3">
+        <v>2</v>
+      </c>
+      <c r="C8" s="3">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3">
+        <v>3</v>
+      </c>
+      <c r="E8" s="4">
+        <v>10</v>
+      </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="3"/>
+      <c r="H8" s="4">
+        <v>4</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="4"/>
+      <c r="B9" s="3">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3">
+        <v>2</v>
+      </c>
+      <c r="D9" s="3">
+        <v>3</v>
+      </c>
+      <c r="E9" s="4">
+        <v>10</v>
+      </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="3"/>
+      <c r="H9" s="4">
+        <v>4</v>
+      </c>
+      <c r="I9" s="4">
+        <v>1</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="4"/>
+      <c r="B10" s="3">
+        <v>2</v>
+      </c>
+      <c r="C10" s="3">
+        <v>3</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4">
+        <v>10</v>
+      </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="3"/>
+      <c r="H10" s="4">
+        <v>4</v>
+      </c>
+      <c r="I10" s="4">
+        <v>1</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="4"/>
+      <c r="B11" s="3">
+        <v>2</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3">
+        <v>3</v>
+      </c>
+      <c r="E11" s="4">
+        <v>10</v>
+      </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="3"/>
+      <c r="H11" s="4">
+        <v>4</v>
+      </c>
+      <c r="I11" s="4">
+        <v>1</v>
+      </c>
+      <c r="J11" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="4"/>
+      <c r="B12" s="3">
+        <v>3</v>
+      </c>
+      <c r="C12" s="3">
+        <v>2</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4">
+        <v>10</v>
+      </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="3"/>
+      <c r="H12" s="4">
+        <v>4</v>
+      </c>
+      <c r="I12" s="4">
+        <v>1</v>
+      </c>
+      <c r="J12" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="4"/>
+      <c r="B13" s="3">
+        <v>2</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3">
+        <v>3</v>
+      </c>
+      <c r="E13" s="4">
+        <v>10</v>
+      </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="3"/>
+      <c r="H13" s="4">
+        <v>4</v>
+      </c>
+      <c r="I13" s="4">
+        <v>1</v>
+      </c>
+      <c r="J13" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="4"/>
+      <c r="B14" s="3">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3">
+        <v>2</v>
+      </c>
+      <c r="D14" s="3">
+        <v>3</v>
+      </c>
+      <c r="E14" s="4">
+        <v>10</v>
+      </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="3"/>
+      <c r="H14" s="4">
+        <v>4</v>
+      </c>
+      <c r="I14" s="4">
+        <v>1</v>
+      </c>
+      <c r="J14" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="4"/>
+      <c r="B15" s="3">
+        <v>2</v>
+      </c>
+      <c r="C15" s="3">
+        <v>3</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4">
+        <v>10</v>
+      </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="3"/>
+      <c r="H15" s="4">
+        <v>4</v>
+      </c>
+      <c r="I15" s="4">
+        <v>1</v>
+      </c>
+      <c r="J15" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="4"/>
+      <c r="B16" s="3">
+        <v>1</v>
+      </c>
+      <c r="C16" s="3">
+        <v>3</v>
+      </c>
+      <c r="D16" s="3">
+        <v>2</v>
+      </c>
+      <c r="E16" s="4">
+        <v>10</v>
+      </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="3"/>
+      <c r="H16" s="4">
+        <v>4</v>
+      </c>
+      <c r="I16" s="4">
+        <v>1</v>
+      </c>
+      <c r="J16" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="4"/>
+      <c r="B17" s="3">
+        <v>3</v>
+      </c>
+      <c r="C17" s="3">
+        <v>2</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4">
+        <v>10</v>
+      </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
+      <c r="H17" s="4">
+        <v>4</v>
+      </c>
+      <c r="I17" s="4">
+        <v>1</v>
+      </c>
       <c r="J17" s="3"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="4"/>
+      <c r="B18" s="3">
+        <v>1</v>
+      </c>
+      <c r="C18" s="3">
+        <v>2</v>
+      </c>
+      <c r="D18" s="3">
+        <v>3</v>
+      </c>
+      <c r="E18" s="4">
+        <v>10</v>
+      </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
+      <c r="H18" s="4">
+        <v>4</v>
+      </c>
+      <c r="I18" s="4">
+        <v>1</v>
+      </c>
       <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="4"/>
+      <c r="B19" s="3">
+        <v>2</v>
+      </c>
+      <c r="C19" s="3">
+        <v>3</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1</v>
+      </c>
+      <c r="E19" s="4">
+        <v>10</v>
+      </c>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
+      <c r="H19" s="4">
+        <v>4</v>
+      </c>
+      <c r="I19" s="4">
+        <v>1</v>
+      </c>
       <c r="J19" s="3"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
+      <c r="B20" s="3">
+        <v>2</v>
+      </c>
+      <c r="C20" s="3">
+        <v>3</v>
+      </c>
+      <c r="D20" s="3">
+        <v>1</v>
+      </c>
+      <c r="E20" s="4">
+        <v>10</v>
+      </c>
+      <c r="F20" s="4">
+        <v>3</v>
+      </c>
       <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
+      <c r="H20" s="4">
+        <v>4</v>
+      </c>
+      <c r="I20" s="4">
+        <v>1</v>
+      </c>
       <c r="J20" s="3"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="4"/>
+      <c r="B21" s="3">
+        <v>1</v>
+      </c>
+      <c r="C21" s="3">
+        <v>3</v>
+      </c>
+      <c r="D21" s="3">
+        <v>2</v>
+      </c>
+      <c r="E21" s="4">
+        <v>10</v>
+      </c>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
+      <c r="H21" s="4">
+        <v>4</v>
+      </c>
+      <c r="I21" s="4">
+        <v>1</v>
+      </c>
       <c r="J21" s="3"/>
     </row>
   </sheetData>
